--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -1910,7 +1910,7 @@
       <c r="L25" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -1956,11 +1956,7 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="L26" s="9" t="inlineStr"/>
       <c r="M26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1999,11 +1995,7 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="L27" s="9" t="inlineStr"/>
       <c r="M27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2760,7 +2752,7 @@
       <c r="L42" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -2802,11 +2794,7 @@
       </c>
       <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="L43" s="9" t="inlineStr"/>
       <c r="M43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2841,11 +2829,7 @@
       </c>
       <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="L44" s="9" t="inlineStr"/>
       <c r="M44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3255,7 +3239,7 @@
       <c r="L53" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -3289,11 +3273,7 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
-      <c r="L54" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="L54" s="9" t="inlineStr"/>
       <c r="M54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
@@ -5289,7 +5269,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5345,7 +5325,11 @@
       </c>
       <c r="B98" s="9" t="inlineStr"/>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>
@@ -5668,7 +5652,7 @@
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5680,7 +5664,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -5729,9 +5713,17 @@
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>🖱右</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>🖱左</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -5764,7 +5756,7 @@
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5776,7 +5768,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -5830,9 +5822,17 @@
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>🖱進</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>🖱戻</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
@@ -7338,7 +7338,7 @@
       <c r="L25" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -7384,11 +7384,7 @@
           <t>&amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="L26" s="9" t="inlineStr"/>
       <c r="M26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
@@ -7427,11 +7423,7 @@
           <t>〃</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="L27" s="9" t="inlineStr"/>
       <c r="M27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
@@ -8223,7 +8215,7 @@
       <c r="L42" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -8265,11 +8257,7 @@
       </c>
       <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="L43" s="9" t="inlineStr"/>
       <c r="M43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
@@ -8304,11 +8292,7 @@
       </c>
       <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="L44" s="9" t="inlineStr"/>
       <c r="M44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
@@ -8730,7 +8714,7 @@
       <c r="L53" s="7" t="inlineStr">
         <is>
           <t>pos 40
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -8764,11 +8748,7 @@
       <c r="I54" s="9" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr"/>
       <c r="K54" s="9" t="inlineStr"/>
-      <c r="L54" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="L54" s="9" t="inlineStr"/>
       <c r="M54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
@@ -10769,7 +10749,7 @@
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -10825,7 +10805,11 @@
       </c>
       <c r="B98" s="9" t="inlineStr"/>
       <c r="C98" s="9" t="inlineStr"/>
-      <c r="D98" s="9" t="inlineStr"/>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo MOUSE_SCROLL</t>
+        </is>
+      </c>
       <c r="E98" s="9" t="inlineStr"/>
       <c r="F98" s="9" t="inlineStr"/>
       <c r="G98" s="9" t="inlineStr"/>
@@ -11148,7 +11132,7 @@
       <c r="C106" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;none</t>
+&amp;mkp MB2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -11160,7 +11144,7 @@
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;mkp MB1</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
@@ -11209,9 +11193,17 @@
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr"/>
-      <c r="C107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB2</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB1</t>
+        </is>
+      </c>
       <c r="F107" s="9" t="inlineStr"/>
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
@@ -11244,7 +11236,7 @@
       <c r="C108" s="7" t="inlineStr">
         <is>
           <t>pos 21
-&amp;none</t>
+&amp;mkp MB5</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -11256,7 +11248,7 @@
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>pos 23
-&amp;none</t>
+&amp;mkp MB4</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -11310,9 +11302,17 @@
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr"/>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB5</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="9" t="inlineStr"/>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mkp MB4</t>
+        </is>
+      </c>
       <c r="F109" s="9" t="inlineStr"/>
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5257,7 +5257,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5313,7 +5313,7 @@
       <c r="M97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
@@ -5342,7 +5346,11 @@
         </is>
       </c>
       <c r="L98" s="9" t="inlineStr"/>
-      <c r="M98" s="9" t="inlineStr"/>
+      <c r="M98" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -5353,7 +5361,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -5414,7 +5422,7 @@
       <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5432,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -5435,7 +5447,11 @@
       <c r="J100" s="9" t="inlineStr"/>
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
-      <c r="M100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -5452,13 +5468,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5518,8 +5534,16 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
@@ -5646,7 +5670,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -5702,7 +5726,7 @@
       <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5736,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>🖱右</t>
@@ -5739,7 +5767,11 @@
           <t>🖱右</t>
         </is>
       </c>
-      <c r="M107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -5750,7 +5782,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -5811,7 +5843,7 @@
       <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5853,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>🖱進</t>
@@ -5848,7 +5884,11 @@
           <t>🖱進</t>
         </is>
       </c>
-      <c r="M109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -5865,13 +5905,13 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -5931,8 +5971,16 @@
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>
@@ -10737,7 +10785,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -10793,7 +10841,7 @@
       <c r="M97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10851,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C98" s="9" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
         <is>
@@ -10822,7 +10874,11 @@
         </is>
       </c>
       <c r="L98" s="9" t="inlineStr"/>
-      <c r="M98" s="9" t="inlineStr"/>
+      <c r="M98" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
@@ -10833,7 +10889,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -10894,7 +10950,7 @@
       <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -10904,7 +10960,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="C100" s="9" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
@@ -10915,7 +10975,11 @@
       <c r="J100" s="9" t="inlineStr"/>
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
-      <c r="M100" s="9" t="inlineStr"/>
+      <c r="M100" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
@@ -10932,13 +10996,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -10998,8 +11062,16 @@
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr"/>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="E102" s="9" t="inlineStr"/>
       <c r="F102" s="9" t="inlineStr"/>
       <c r="G102" s="9" t="inlineStr"/>
@@ -11126,7 +11198,7 @@
       <c r="B106" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -11182,7 +11254,7 @@
       <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11264,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB2</t>
@@ -11219,7 +11295,11 @@
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="M107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
@@ -11230,7 +11310,7 @@
       <c r="B108" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
@@ -11291,7 +11371,7 @@
       <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11381,11 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB5</t>
@@ -11328,7 +11412,11 @@
           <t>&amp;mkp MB5</t>
         </is>
       </c>
-      <c r="M109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
@@ -11345,13 +11433,13 @@
       <c r="C110" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -11411,8 +11499,16 @@
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr"/>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="E111" s="9" t="inlineStr"/>
       <c r="F111" s="9" t="inlineStr"/>
       <c r="G111" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5257,7 +5257,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -5313,7 +5313,7 @@
       <c r="M97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>LCtrl</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr"/>
@@ -5348,7 +5348,7 @@
       <c r="L98" s="9" t="inlineStr"/>
       <c r="M98" s="9" t="inlineStr">
         <is>
-          <t>RCtrl</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -5422,7 +5422,7 @@
       <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>LShift</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr"/>
@@ -5449,7 +5449,7 @@
       <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr">
         <is>
-          <t>RShift</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -5468,13 +5468,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -5536,12 +5536,12 @@
       <c r="B102" s="9" t="inlineStr"/>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>LWin</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>LAlt</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr"/>
@@ -10785,7 +10785,7 @@
       <c r="B97" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -10841,7 +10841,7 @@
       <c r="M97" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LCTRL</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr"/>
@@ -10876,7 +10876,7 @@
       <c r="L98" s="9" t="inlineStr"/>
       <c r="M98" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RCTRL</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       <c r="B99" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -10950,7 +10950,7 @@
       <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr"/>
@@ -10977,7 +10977,7 @@
       <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
     </row>
@@ -10996,13 +10996,13 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>pos 32
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
           <t>pos 33
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
@@ -11064,12 +11064,12 @@
       <c r="B102" s="9" t="inlineStr"/>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_WIN</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_ALT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -549,11 +549,12 @@
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -623,6 +624,11 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -643,7 +649,8 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="5" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -683,31 +690,32 @@
       </c>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp P</t>
@@ -747,27 +755,28 @@
       </c>
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -811,31 +820,32 @@
       </c>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp H</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp J</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp K</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp L</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;mt RCTRL MINUS</t>
@@ -875,27 +885,28 @@
       </c>
       <c r="G8" s="9" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -934,11 +945,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I9" s="9" t="inlineStr"/>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -955,6 +962,11 @@
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -1005,29 +1017,35 @@
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;kp N</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;kp M</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;kp COMMA</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;kp PERIOD</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;mt RIGHT_SHIFT SLASH</t>
@@ -1073,25 +1091,30 @@
       <c r="H11" s="9" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr">
         <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>.</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>/</t>
         </is>
@@ -1156,6 +1179,11 @@
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
           <t>RShift</t>
         </is>
       </c>
@@ -1205,29 +1233,25 @@
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;mo VIM_NORMAL_BASE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;mo BLUETOOTH</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;mo VIM_NORMAL_BASE</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;mo FUNCTION</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;mo FUNCTION</t>
@@ -1273,25 +1297,22 @@
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
           <t>ENTER</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>L7</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>L6</t>
         </is>
       </c>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>L6</t>
         </is>
@@ -1336,25 +1357,22 @@
       <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr">
         <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
       <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1377,7 +1395,8 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
-      <c r="M16" s="5" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -1417,31 +1436,32 @@
       </c>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp N0</t>
@@ -1481,27 +1501,28 @@
       </c>
       <c r="G18" s="9" t="inlineStr"/>
       <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1545,31 +1566,32 @@
       </c>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp BACKSPACE</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp SEMICOLON</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp BACKSLASH</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -1609,27 +1631,28 @@
       </c>
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>;</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>'</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>\</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -1668,11 +1691,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I21" s="9" t="inlineStr"/>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1689,6 +1708,11 @@
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1739,29 +1763,35 @@
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;kp EQUAL</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;trans</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;trans</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;trans</t>
@@ -1786,22 +1816,23 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="9" t="inlineStr"/>
       <c r="I23" s="9" t="inlineStr"/>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -1825,11 +1856,7 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="9" t="inlineStr"/>
       <c r="I24" s="9" t="inlineStr"/>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="J24" s="9" t="inlineStr"/>
       <c r="K24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -1841,6 +1868,11 @@
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -1891,29 +1923,25 @@
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
           <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -1949,15 +1977,16 @@
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
-      <c r="I26" s="9" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
       <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
+      <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
       <c r="M26" s="9" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1988,15 +2017,16 @@
       </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr"/>
-      <c r="I27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
       <c r="M27" s="9" t="inlineStr"/>
+      <c r="N27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2015,7 +2045,8 @@
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
-      <c r="M28" s="5" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -2055,31 +2086,32 @@
       </c>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LC(V)</t>
@@ -2108,19 +2140,20 @@
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
       <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>⌃Z</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr"/>
-      <c r="L30" s="10" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ ENTER</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>⌃V</t>
         </is>
@@ -2147,25 +2180,26 @@
       <c r="F31" s="9" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ⇧END
 ▸ ⌃C</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr"/>
       <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2192,26 +2226,27 @@
       <c r="F32" s="9" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>⇧END
 ▸ ⌃C</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K32" s="9" t="inlineStr"/>
-      <c r="L32" s="10" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>HOME
 ▸ ENTER
 ▸ ↑</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2243,18 +2278,19 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="inlineStr"/>
       <c r="I33" s="9" t="inlineStr"/>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>PgUp</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr"/>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="L33" s="9" t="inlineStr"/>
       <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2298,31 +2334,32 @@
       </c>
       <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mm_vim_j</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp UP_ARROW</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp RIGHT</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -2346,27 +2383,28 @@
       <c r="F35" s="9" t="inlineStr"/>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="9" t="inlineStr"/>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>←</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>→</t>
         </is>
       </c>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -2399,11 +2437,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -2420,6 +2454,11 @@
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2451,29 +2490,30 @@
       </c>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>END
 ▸ DEL
 ▸ SPACE</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2500,11 +2540,7 @@
       <c r="F38" s="9" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -2521,6 +2557,11 @@
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2571,29 +2612,35 @@
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;mm_vim_n</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr">
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -2629,15 +2676,16 @@
       </c>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="9" t="inlineStr"/>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr"/>
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr"/>
       <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr"/>
+      <c r="N40" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -2674,15 +2722,16 @@
       </c>
       <c r="G41" s="9" t="inlineStr"/>
       <c r="H41" s="9" t="inlineStr"/>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr"/>
+      <c r="I41" s="9" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="K41" s="9" t="inlineStr"/>
       <c r="L41" s="9" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr"/>
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -2733,29 +2782,25 @@
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="N42" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -2787,15 +2832,16 @@
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>ENTER</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
       <c r="M43" s="9" t="inlineStr"/>
+      <c r="N43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -2822,15 +2868,16 @@
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr"/>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
       <c r="M44" s="9" t="inlineStr"/>
+      <c r="N44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2849,7 +2896,8 @@
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
-      <c r="M45" s="5" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="5" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -2889,31 +2937,32 @@
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr">
+      <c r="N46" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp HOME</t>
@@ -2937,7 +2986,8 @@
       <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr"/>
       <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr">
+      <c r="M47" s="9" t="inlineStr"/>
+      <c r="N47" s="9" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
@@ -2960,15 +3010,16 @@
       <c r="F48" s="9" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr"/>
-      <c r="I48" s="9" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>HOME</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr"/>
       <c r="L48" s="9" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr">
+      <c r="M48" s="9" t="inlineStr"/>
+      <c r="N48" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -3012,31 +3063,32 @@
       </c>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr">
+      <c r="N49" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -3060,15 +3112,16 @@
       <c r="F50" s="9" t="inlineStr"/>
       <c r="G50" s="9" t="inlineStr"/>
       <c r="H50" s="9" t="inlineStr"/>
-      <c r="I50" s="9" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>←</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr"/>
       <c r="K50" s="9" t="inlineStr"/>
       <c r="L50" s="9" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr">
+      <c r="M50" s="9" t="inlineStr"/>
+      <c r="N50" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -3119,29 +3172,35 @@
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr">
+      <c r="N51" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -3169,7 +3228,8 @@
       <c r="J52" s="9" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="9" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr">
+      <c r="M52" s="9" t="inlineStr"/>
+      <c r="N52" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -3220,29 +3280,25 @@
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr">
+      <c r="N53" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -3275,6 +3331,7 @@
       <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="9" t="inlineStr"/>
       <c r="M54" s="9" t="inlineStr"/>
+      <c r="N54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -3293,7 +3350,8 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="5" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="5" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -3333,31 +3391,32 @@
       </c>
       <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L56" s="7" t="inlineStr">
+      <c r="M56" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M56" s="7" t="inlineStr">
+      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;macro_vim_visual_p</t>
@@ -3385,7 +3444,8 @@
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr"/>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I57" s="9" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -3394,10 +3454,10 @@
 ▸ ⇒BASE_QWERTY</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr"/>
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr">
+      <c r="M57" s="9" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>LShift
 ▸ RShift
@@ -3444,31 +3504,32 @@
       </c>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="J58" s="7" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp LS(UP)</t>
         </is>
       </c>
-      <c r="L58" s="7" t="inlineStr">
+      <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
-      <c r="M58" s="7" t="inlineStr">
+      <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -3499,27 +3560,28 @@
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr"/>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="I59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>⇧←</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>⇧↓</t>
         </is>
       </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>⇧↑</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="M59" s="9" t="inlineStr">
         <is>
           <t>⇧→</t>
         </is>
       </c>
-      <c r="M59" s="9" t="inlineStr">
+      <c r="N59" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -3550,11 +3612,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr"/>
       <c r="H60" s="9" t="inlineStr"/>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -3571,6 +3629,11 @@
         </is>
       </c>
       <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -3601,11 +3664,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr"/>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I61" s="9" t="inlineStr"/>
       <c r="J61" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -3622,6 +3681,11 @@
         </is>
       </c>
       <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -3672,29 +3736,35 @@
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;kp F3</t>
         </is>
       </c>
-      <c r="J62" s="7" t="inlineStr">
+      <c r="K62" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K62" s="7" t="inlineStr">
+      <c r="L62" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L62" s="7" t="inlineStr">
+      <c r="M62" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M62" s="7" t="inlineStr">
+      <c r="N62" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -3736,15 +3806,16 @@
       </c>
       <c r="G63" s="9" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr"/>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="I63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr">
         <is>
           <t>F3</t>
         </is>
       </c>
-      <c r="J63" s="9" t="inlineStr"/>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr">
+      <c r="M63" s="9" t="inlineStr"/>
+      <c r="N63" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -3795,29 +3866,25 @@
       <c r="H64" s="7" t="inlineStr"/>
       <c r="I64" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
-      <c r="J64" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M64" s="7" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -3841,15 +3908,16 @@
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr"/>
-      <c r="I65" s="9" t="inlineStr">
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr"/>
       <c r="K65" s="9" t="inlineStr"/>
       <c r="L65" s="9" t="inlineStr"/>
       <c r="M65" s="9" t="inlineStr"/>
+      <c r="N65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -3868,7 +3936,8 @@
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
-      <c r="M66" s="5" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -3908,31 +3977,32 @@
       </c>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
-      <c r="J67" s="7" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K67" s="7" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M67" s="7" t="inlineStr">
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LS(HOME)</t>
@@ -3956,7 +4026,8 @@
       <c r="J68" s="9" t="inlineStr"/>
       <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
         <is>
           <t>⇧HOME</t>
         </is>
@@ -3979,15 +4050,16 @@
       <c r="F69" s="9" t="inlineStr"/>
       <c r="G69" s="9" t="inlineStr"/>
       <c r="H69" s="9" t="inlineStr"/>
-      <c r="I69" s="9" t="inlineStr">
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>⇧HOME</t>
         </is>
       </c>
-      <c r="J69" s="9" t="inlineStr"/>
       <c r="K69" s="9" t="inlineStr"/>
       <c r="L69" s="9" t="inlineStr"/>
-      <c r="M69" s="9" t="inlineStr">
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -4031,31 +4103,32 @@
       </c>
       <c r="G70" s="7" t="inlineStr"/>
       <c r="H70" s="7" t="inlineStr"/>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr"/>
+      <c r="J70" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="J70" s="7" t="inlineStr">
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K70" s="7" t="inlineStr">
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L70" s="7" t="inlineStr">
+      <c r="M70" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M70" s="7" t="inlineStr">
+      <c r="N70" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -4079,15 +4152,16 @@
       <c r="F71" s="9" t="inlineStr"/>
       <c r="G71" s="9" t="inlineStr"/>
       <c r="H71" s="9" t="inlineStr"/>
-      <c r="I71" s="9" t="inlineStr">
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>⇧←</t>
         </is>
       </c>
-      <c r="J71" s="9" t="inlineStr"/>
       <c r="K71" s="9" t="inlineStr"/>
       <c r="L71" s="9" t="inlineStr"/>
-      <c r="M71" s="9" t="inlineStr">
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -4138,29 +4212,35 @@
       <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J72" s="7" t="inlineStr">
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K72" s="7" t="inlineStr">
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L72" s="7" t="inlineStr">
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M72" s="7" t="inlineStr">
+      <c r="N72" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -4188,7 +4268,8 @@
       <c r="J73" s="9" t="inlineStr"/>
       <c r="K73" s="9" t="inlineStr"/>
       <c r="L73" s="9" t="inlineStr"/>
-      <c r="M73" s="9" t="inlineStr">
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -4239,29 +4320,25 @@
       <c r="H74" s="7" t="inlineStr"/>
       <c r="I74" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K74" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M74" s="7" t="inlineStr">
+      <c r="N74" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -4286,6 +4363,7 @@
       <c r="K75" s="9" t="inlineStr"/>
       <c r="L75" s="9" t="inlineStr"/>
       <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -4304,7 +4382,8 @@
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
-      <c r="M76" s="5" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="5" t="n"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
@@ -4344,31 +4423,32 @@
       </c>
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
-      <c r="J77" s="7" t="inlineStr">
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
-      <c r="K77" s="7" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
-      <c r="M77" s="7" t="inlineStr">
+      <c r="N77" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp F10</t>
@@ -4408,27 +4488,28 @@
       </c>
       <c r="G78" s="9" t="inlineStr"/>
       <c r="H78" s="9" t="inlineStr"/>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>F6</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>F7</t>
         </is>
       </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
-      <c r="L78" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>F9</t>
         </is>
       </c>
-      <c r="M78" s="9" t="inlineStr">
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>F10</t>
         </is>
@@ -4472,31 +4553,32 @@
       </c>
       <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr"/>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J79" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K79" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="M79" s="7" t="inlineStr">
+      <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -4523,12 +4605,13 @@
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
-      <c r="L80" s="9" t="inlineStr">
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4575,29 +4658,35 @@
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="J81" s="7" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K81" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L81" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M81" s="7" t="inlineStr">
+      <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -4621,15 +4710,16 @@
       </c>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
-      <c r="I82" s="9" t="inlineStr">
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>ブートローダ</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -4676,29 +4766,25 @@
       <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J83" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M83" s="7" t="inlineStr">
+      <c r="N83" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -4723,6 +4809,7 @@
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
+      <c r="N84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -4741,7 +4828,8 @@
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="n"/>
       <c r="L85" s="4" t="n"/>
-      <c r="M85" s="5" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="5" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -4781,31 +4869,32 @@
       </c>
       <c r="G86" s="7" t="inlineStr"/>
       <c r="H86" s="7" t="inlineStr"/>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="J86" s="7" t="inlineStr">
+      <c r="K86" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
-      <c r="K86" s="7" t="inlineStr">
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L86" s="7" t="inlineStr">
+      <c r="M86" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M86" s="7" t="inlineStr">
+      <c r="N86" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -4846,14 +4935,15 @@
       <c r="G87" s="9" t="inlineStr"/>
       <c r="H87" s="9" t="inlineStr"/>
       <c r="I87" s="9" t="inlineStr"/>
-      <c r="J87" s="9" t="inlineStr">
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr">
         <is>
           <t>USB出力</t>
         </is>
       </c>
-      <c r="K87" s="9" t="inlineStr"/>
       <c r="L87" s="9" t="inlineStr"/>
       <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
@@ -4893,31 +4983,32 @@
       </c>
       <c r="G88" s="7" t="inlineStr"/>
       <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J88" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K88" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L88" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M88" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -4946,6 +5037,7 @@
       <c r="K89" s="9" t="inlineStr"/>
       <c r="L89" s="9" t="inlineStr"/>
       <c r="M89" s="9" t="inlineStr"/>
+      <c r="N89" s="9" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
@@ -4992,29 +5084,35 @@
       <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J90" s="7" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K90" s="7" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L90" s="7" t="inlineStr">
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M90" s="7" t="inlineStr">
+      <c r="N90" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -5047,6 +5145,7 @@
       <c r="K91" s="9" t="inlineStr"/>
       <c r="L91" s="9" t="inlineStr"/>
       <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
@@ -5093,29 +5192,25 @@
       <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J92" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K92" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M92" s="7" t="inlineStr">
+      <c r="N92" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -5140,6 +5235,7 @@
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
       <c r="M93" s="9" t="inlineStr"/>
+      <c r="N93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -5158,7 +5254,8 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="4" t="n"/>
-      <c r="M94" s="5" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="5" t="n"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
@@ -5198,31 +5295,32 @@
       </c>
       <c r="G95" s="7" t="inlineStr"/>
       <c r="H95" s="7" t="inlineStr"/>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="J95" s="7" t="inlineStr">
+      <c r="K95" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K95" s="7" t="inlineStr">
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L95" s="7" t="inlineStr">
+      <c r="M95" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M95" s="7" t="inlineStr">
+      <c r="N95" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -5247,6 +5345,7 @@
       <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
@@ -5286,31 +5385,32 @@
       </c>
       <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J97" s="7" t="inlineStr">
+      <c r="K97" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K97" s="7" t="inlineStr">
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
-      <c r="L97" s="7" t="inlineStr">
+      <c r="M97" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M97" s="7" t="inlineStr">
+      <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -5340,13 +5440,14 @@
       <c r="H98" s="9" t="inlineStr"/>
       <c r="I98" s="9" t="inlineStr"/>
       <c r="J98" s="9" t="inlineStr"/>
-      <c r="K98" s="9" t="inlineStr">
+      <c r="K98" s="9" t="inlineStr"/>
+      <c r="L98" s="9" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
       </c>
-      <c r="L98" s="9" t="inlineStr"/>
-      <c r="M98" s="9" t="inlineStr">
+      <c r="M98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -5397,29 +5498,35 @@
       <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J99" s="7" t="inlineStr">
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K99" s="7" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L99" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M99" s="7" t="inlineStr">
+      <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;trans</t>
@@ -5447,7 +5554,8 @@
       <c r="J100" s="9" t="inlineStr"/>
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
-      <c r="M100" s="9" t="inlineStr">
+      <c r="M100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -5498,29 +5606,25 @@
       <c r="H101" s="7" t="inlineStr"/>
       <c r="I101" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J101" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K101" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L101" s="7" t="inlineStr">
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M101" s="7" t="inlineStr">
+      <c r="N101" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -5553,6 +5657,7 @@
       <c r="K102" s="9" t="inlineStr"/>
       <c r="L102" s="9" t="inlineStr"/>
       <c r="M102" s="9" t="inlineStr"/>
+      <c r="N102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -5571,7 +5676,8 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
       <c r="L103" s="4" t="n"/>
-      <c r="M103" s="5" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="5" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
@@ -5611,31 +5717,32 @@
       </c>
       <c r="G104" s="7" t="inlineStr"/>
       <c r="H104" s="7" t="inlineStr"/>
-      <c r="I104" s="7" t="inlineStr">
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="J104" s="7" t="inlineStr">
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K104" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L104" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M104" s="7" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -5660,6 +5767,7 @@
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
       <c r="M105" s="9" t="inlineStr"/>
+      <c r="N105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -5699,31 +5807,32 @@
       </c>
       <c r="G106" s="7" t="inlineStr"/>
       <c r="H106" s="7" t="inlineStr"/>
-      <c r="I106" s="7" t="inlineStr">
+      <c r="I106" s="7" t="inlineStr"/>
+      <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J106" s="7" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mkp MB1</t>
         </is>
       </c>
-      <c r="K106" s="7" t="inlineStr">
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L106" s="7" t="inlineStr">
+      <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;mkp MB2</t>
         </is>
       </c>
-      <c r="M106" s="7" t="inlineStr">
+      <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -5756,18 +5865,19 @@
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
       <c r="I107" s="9" t="inlineStr"/>
-      <c r="J107" s="9" t="inlineStr">
+      <c r="J107" s="9" t="inlineStr"/>
+      <c r="K107" s="9" t="inlineStr">
         <is>
           <t>🖱左</t>
         </is>
       </c>
-      <c r="K107" s="9" t="inlineStr"/>
-      <c r="L107" s="9" t="inlineStr">
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr">
         <is>
           <t>🖱右</t>
         </is>
       </c>
-      <c r="M107" s="9" t="inlineStr">
+      <c r="N107" s="9" t="inlineStr">
         <is>
           <t>RCtrl</t>
         </is>
@@ -5818,29 +5928,35 @@
       <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J108" s="7" t="inlineStr">
+      <c r="K108" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;mkp MB4</t>
         </is>
       </c>
-      <c r="K108" s="7" t="inlineStr">
+      <c r="L108" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L108" s="7" t="inlineStr">
+      <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;mkp MB5</t>
         </is>
       </c>
-      <c r="M108" s="7" t="inlineStr">
+      <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -5873,18 +5989,19 @@
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
       <c r="I109" s="9" t="inlineStr"/>
-      <c r="J109" s="9" t="inlineStr">
+      <c r="J109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr">
         <is>
           <t>🖱戻</t>
         </is>
       </c>
-      <c r="K109" s="9" t="inlineStr"/>
-      <c r="L109" s="9" t="inlineStr">
+      <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr">
         <is>
           <t>🖱進</t>
         </is>
       </c>
-      <c r="M109" s="9" t="inlineStr">
+      <c r="N109" s="9" t="inlineStr">
         <is>
           <t>RShift</t>
         </is>
@@ -5935,29 +6052,25 @@
       <c r="H110" s="7" t="inlineStr"/>
       <c r="I110" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J110" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K110" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L110" s="7" t="inlineStr">
+      <c r="K110" s="7" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M110" s="7" t="inlineStr">
+      <c r="N110" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -5990,19 +6103,20 @@
       <c r="K111" s="9" t="inlineStr"/>
       <c r="L111" s="9" t="inlineStr"/>
       <c r="M111" s="9" t="inlineStr"/>
+      <c r="N111" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A76:M76"/>
-    <mergeCell ref="A66:M66"/>
-    <mergeCell ref="A45:M45"/>
-    <mergeCell ref="A94:M94"/>
-    <mergeCell ref="A103:M103"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A85:M85"/>
-    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A55:N55"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A85:N85"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A103:N103"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A94:N94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6014,7 +6128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6025,11 +6139,12 @@
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6099,6 +6214,11 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6239,8 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="5" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -6159,31 +6280,32 @@
       </c>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp Y</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp U</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp I</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp O</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp P</t>
@@ -6223,27 +6345,28 @@
       </c>
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp Y</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp U</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp I</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp O</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>&amp;kp P</t>
         </is>
@@ -6287,31 +6410,32 @@
       </c>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp H</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp J</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp K</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp L</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;mt RCTRL MINUS</t>
@@ -6351,27 +6475,28 @@
       </c>
       <c r="G8" s="9" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>&amp;kp H</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>&amp;kp J</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>&amp;kp K</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>&amp;kp L</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RCTRL MINUS</t>
         </is>
@@ -6410,11 +6535,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I9" s="9" t="inlineStr"/>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -6431,6 +6552,11 @@
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RCTRL MINUS</t>
         </is>
@@ -6481,29 +6607,35 @@
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;kp N</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;kp M</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;kp COMMA</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;kp PERIOD</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;mt RIGHT_SHIFT SLASH</t>
@@ -6549,25 +6681,30 @@
       <c r="H11" s="9" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr">
         <is>
+          <t>&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
           <t>&amp;kp N</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>&amp;kp M</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>&amp;kp COMMA</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>&amp;kp PERIOD</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>&amp;mt RIGHT_SHIFT SLASH</t>
         </is>
@@ -6632,6 +6769,11 @@
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
           <t>&amp;mt RIGHT_SHIFT SLASH</t>
         </is>
       </c>
@@ -6681,29 +6823,25 @@
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;mo VIM_NORMAL_BASE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;mo BLUETOOTH</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;mo VIM_NORMAL_BASE</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;mo FUNCTION</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;mo FUNCTION</t>
@@ -6749,25 +6887,22 @@
       <c r="H14" s="9" t="inlineStr"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
+          <t>&amp;mo VIM_NORMAL_BASE</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
           <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo BLUETOOTH</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_NORMAL_BASE</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>&amp;mo FUNCTION</t>
         </is>
       </c>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>&amp;mo FUNCTION</t>
         </is>
@@ -6812,25 +6947,22 @@
       <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr">
         <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
           <t>&amp;lt NUM_SYMBOL ENTER</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
       <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -6853,7 +6985,8 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
-      <c r="M16" s="5" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="5" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -6893,31 +7026,32 @@
       </c>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp N6</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp N7</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp N8</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp N9</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp N0</t>
@@ -6957,27 +7091,28 @@
       </c>
       <c r="G18" s="9" t="inlineStr"/>
       <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N6</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N7</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N8</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N9</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>&amp;kp N0</t>
         </is>
@@ -7021,31 +7156,32 @@
       </c>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp BACKSPACE</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp SEMICOLON</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp BACKSLASH</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -7085,27 +7221,28 @@
       </c>
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>&amp;kp BACKSPACE</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>&amp;kp SEMICOLON</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>&amp;kp SINGLE_QUOTE</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>&amp;kp BACKSLASH</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -7144,11 +7281,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I21" s="9" t="inlineStr"/>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7165,6 +7298,11 @@
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7215,29 +7353,35 @@
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;kp EQUAL</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;trans</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;trans</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;trans</t>
@@ -7262,22 +7406,23 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="9" t="inlineStr"/>
       <c r="I23" s="9" t="inlineStr"/>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>&amp;kp EQUAL</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -7301,11 +7446,7 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="9" t="inlineStr"/>
       <c r="I24" s="9" t="inlineStr"/>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="J24" s="9" t="inlineStr"/>
       <c r="K24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7317,6 +7458,11 @@
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7367,29 +7513,25 @@
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>pos 37
-&amp;none</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
           <t>pos 39
 &amp;mo VIM_NORMAL_SYM</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>pos 37
+&amp;none</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -7425,15 +7567,16 @@
       </c>
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="inlineStr"/>
-      <c r="I26" s="9" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo VIM_NORMAL_SYM</t>
+        </is>
+      </c>
       <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>&amp;mo VIM_NORMAL_SYM</t>
-        </is>
-      </c>
+      <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr"/>
       <c r="M26" s="9" t="inlineStr"/>
+      <c r="N26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -7464,15 +7607,16 @@
       </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr"/>
-      <c r="I27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K27" s="9" t="inlineStr"/>
       <c r="L27" s="9" t="inlineStr"/>
       <c r="M27" s="9" t="inlineStr"/>
+      <c r="N27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -7491,7 +7635,8 @@
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
-      <c r="M28" s="5" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="5" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -7531,31 +7676,32 @@
       </c>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_y</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;mm_vim_u</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;mm_vim_o</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LC(V)</t>
@@ -7589,27 +7735,28 @@
       <c r="F30" s="9" t="inlineStr"/>
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[0]
 ▸ &amp;none</t>
         </is>
       </c>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[0]
 ▸ &amp;kp LC(Z)</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr"/>
-      <c r="L30" s="10" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[0]
 ▸ macro_vim_o</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LC(V)</t>
         </is>
@@ -7636,25 +7783,26 @@
       <c r="F31" s="9" t="inlineStr"/>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[0]
 ▸ td_vim_y[1]
 ▸ macro_vim_yy</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr"/>
       <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7681,25 +7829,26 @@
       <c r="F32" s="9" t="inlineStr"/>
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_y[1]
 ▸ macro_vim_shift_y</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="K32" s="9" t="inlineStr"/>
-      <c r="L32" s="10" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>mm_vim_o[1]
 ▸ macro_vim_shift_o</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7733,19 +7882,20 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="inlineStr"/>
       <c r="I33" s="9" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr"/>
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>mm_vim_u[1]
 ▸ &amp;kp PAGE_UP</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr"/>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="L33" s="9" t="inlineStr"/>
       <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7789,31 +7939,32 @@
       </c>
       <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mm_vim_j</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp UP_ARROW</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp RIGHT</t>
         </is>
       </c>
-      <c r="M34" s="7" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -7850,28 +8001,29 @@
       </c>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="9" t="inlineStr"/>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LEFT</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[0]
 ▸ &amp;kp DOWN</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp UP_ARROW</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT</t>
         </is>
       </c>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -7907,11 +8059,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="9" t="inlineStr"/>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I36" s="9" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -7928,6 +8076,11 @@
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -7961,28 +8114,29 @@
       </c>
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="9" t="inlineStr"/>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>mm_vim_j[1]
 ▸ macro_vim_join</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
       </c>
       <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -8010,11 +8164,7 @@
       <c r="F38" s="9" t="inlineStr"/>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="9" t="inlineStr"/>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I38" s="9" t="inlineStr"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -8031,6 +8181,11 @@
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -8081,29 +8236,35 @@
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;mm_vim_n</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr">
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -8140,16 +8301,17 @@
       </c>
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="9" t="inlineStr"/>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr"/>
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>mm_vim_n[0]
 ▸ &amp;kp F3</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr"/>
       <c r="K40" s="9" t="inlineStr"/>
       <c r="L40" s="9" t="inlineStr"/>
-      <c r="M40" s="9" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr"/>
+      <c r="N40" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -8185,15 +8347,16 @@
       </c>
       <c r="G41" s="9" t="inlineStr"/>
       <c r="H41" s="9" t="inlineStr"/>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr"/>
+      <c r="I41" s="9" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="K41" s="9" t="inlineStr"/>
       <c r="L41" s="9" t="inlineStr"/>
-      <c r="M41" s="9" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr"/>
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -8244,29 +8407,25 @@
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="N42" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -8298,15 +8457,16 @@
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
       <c r="M43" s="9" t="inlineStr"/>
+      <c r="N43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -8333,15 +8493,16 @@
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr"/>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>&amp;lt VIM_NORMAL_SYM ENTER</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
       <c r="M44" s="9" t="inlineStr"/>
+      <c r="N44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -8360,7 +8521,8 @@
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
-      <c r="M45" s="5" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="5" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -8400,31 +8562,32 @@
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_shift_6</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr">
+      <c r="N46" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp HOME</t>
@@ -8449,16 +8612,17 @@
       <c r="F47" s="9" t="inlineStr"/>
       <c r="G47" s="9" t="inlineStr"/>
       <c r="H47" s="9" t="inlineStr"/>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I47" s="9" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[0]
 ▸ &amp;none</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr"/>
       <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="9" t="inlineStr">
+      <c r="M47" s="9" t="inlineStr"/>
+      <c r="N47" s="9" t="inlineStr">
         <is>
           <t>&amp;kp HOME</t>
         </is>
@@ -8482,16 +8646,17 @@
       <c r="F48" s="9" t="inlineStr"/>
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr"/>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>mm_vim_shift_6[1]
 ▸ &amp;kp HOME</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr"/>
       <c r="L48" s="9" t="inlineStr"/>
-      <c r="M48" s="9" t="inlineStr">
+      <c r="M48" s="9" t="inlineStr"/>
+      <c r="N48" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -8535,31 +8700,32 @@
       </c>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LEFT</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr">
+      <c r="N49" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -8583,15 +8749,16 @@
       <c r="F50" s="9" t="inlineStr"/>
       <c r="G50" s="9" t="inlineStr"/>
       <c r="H50" s="9" t="inlineStr"/>
-      <c r="I50" s="9" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LEFT</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr"/>
       <c r="K50" s="9" t="inlineStr"/>
       <c r="L50" s="9" t="inlineStr"/>
-      <c r="M50" s="9" t="inlineStr">
+      <c r="M50" s="9" t="inlineStr"/>
+      <c r="N50" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -8642,29 +8809,35 @@
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr">
+      <c r="N51" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -8692,7 +8865,8 @@
       <c r="J52" s="9" t="inlineStr"/>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="9" t="inlineStr"/>
-      <c r="M52" s="9" t="inlineStr">
+      <c r="M52" s="9" t="inlineStr"/>
+      <c r="N52" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -8743,29 +8917,25 @@
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr">
+      <c r="N53" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -8798,6 +8968,7 @@
       <c r="K54" s="9" t="inlineStr"/>
       <c r="L54" s="9" t="inlineStr"/>
       <c r="M54" s="9" t="inlineStr"/>
+      <c r="N54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -8816,7 +8987,8 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="5" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="5" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -8856,31 +9028,32 @@
       </c>
       <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;macro_vim_visual_y</t>
         </is>
       </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L56" s="7" t="inlineStr">
+      <c r="M56" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M56" s="7" t="inlineStr">
+      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;macro_vim_visual_p</t>
@@ -8908,15 +9081,16 @@
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr"/>
-      <c r="I57" s="9" t="inlineStr">
+      <c r="I57" s="9" t="inlineStr"/>
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>macro_vim_visual_y</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr"/>
       <c r="K57" s="9" t="inlineStr"/>
       <c r="L57" s="9" t="inlineStr"/>
-      <c r="M57" s="9" t="inlineStr">
+      <c r="M57" s="9" t="inlineStr"/>
+      <c r="N57" s="9" t="inlineStr">
         <is>
           <t>macro_vim_visual_p</t>
         </is>
@@ -8960,31 +9134,32 @@
       </c>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="J58" s="7" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;kp LS(DOWN)</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;kp LS(UP)</t>
         </is>
       </c>
-      <c r="L58" s="7" t="inlineStr">
+      <c r="M58" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;kp LS(RIGHT)</t>
         </is>
       </c>
-      <c r="M58" s="7" t="inlineStr">
+      <c r="N58" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -9018,27 +9193,28 @@
       </c>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr"/>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="I59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(DOWN)</t>
         </is>
       </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(UP)</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="M59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(RIGHT)</t>
         </is>
       </c>
-      <c r="M59" s="9" t="inlineStr">
+      <c r="N59" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -9071,11 +9247,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr"/>
       <c r="H60" s="9" t="inlineStr"/>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -9092,6 +9264,11 @@
         </is>
       </c>
       <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -9123,11 +9300,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr"/>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="I61" s="9" t="inlineStr"/>
       <c r="J61" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -9144,6 +9317,11 @@
         </is>
       </c>
       <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -9194,29 +9372,35 @@
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;kp F3</t>
         </is>
       </c>
-      <c r="J62" s="7" t="inlineStr">
+      <c r="K62" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K62" s="7" t="inlineStr">
+      <c r="L62" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L62" s="7" t="inlineStr">
+      <c r="M62" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M62" s="7" t="inlineStr">
+      <c r="N62" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -9252,15 +9436,16 @@
       </c>
       <c r="G63" s="9" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr"/>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="I63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F3</t>
         </is>
       </c>
-      <c r="J63" s="9" t="inlineStr"/>
       <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="9" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr">
+      <c r="M63" s="9" t="inlineStr"/>
+      <c r="N63" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -9311,29 +9496,25 @@
       <c r="H64" s="7" t="inlineStr"/>
       <c r="I64" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
-      <c r="J64" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M64" s="7" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -9357,15 +9538,16 @@
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr"/>
-      <c r="I65" s="9" t="inlineStr">
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>&amp;mo VIM_VISUAL_SYM</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr"/>
       <c r="K65" s="9" t="inlineStr"/>
       <c r="L65" s="9" t="inlineStr"/>
       <c r="M65" s="9" t="inlineStr"/>
+      <c r="N65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -9384,7 +9566,8 @@
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
-      <c r="M66" s="5" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="5" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -9424,31 +9607,32 @@
       </c>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;mm_vim_visual_shift_6</t>
         </is>
       </c>
-      <c r="J67" s="7" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K67" s="7" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M67" s="7" t="inlineStr">
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp LS(HOME)</t>
@@ -9473,16 +9657,17 @@
       <c r="F68" s="9" t="inlineStr"/>
       <c r="G68" s="9" t="inlineStr"/>
       <c r="H68" s="9" t="inlineStr"/>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="I68" s="9" t="inlineStr"/>
+      <c r="J68" s="10" t="inlineStr">
         <is>
           <t>mm_vim_visual_shift_6[0]
 ▸ &amp;none</t>
         </is>
       </c>
-      <c r="J68" s="9" t="inlineStr"/>
       <c r="K68" s="9" t="inlineStr"/>
       <c r="L68" s="9" t="inlineStr"/>
-      <c r="M68" s="9" t="inlineStr">
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(HOME)</t>
         </is>
@@ -9506,16 +9691,17 @@
       <c r="F69" s="9" t="inlineStr"/>
       <c r="G69" s="9" t="inlineStr"/>
       <c r="H69" s="9" t="inlineStr"/>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr">
         <is>
           <t>mm_vim_visual_shift_6[1]
 ▸ &amp;kp LS(HOME)</t>
         </is>
       </c>
-      <c r="J69" s="9" t="inlineStr"/>
       <c r="K69" s="9" t="inlineStr"/>
       <c r="L69" s="9" t="inlineStr"/>
-      <c r="M69" s="9" t="inlineStr">
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
         <is>
           <t>〃</t>
         </is>
@@ -9559,31 +9745,32 @@
       </c>
       <c r="G70" s="7" t="inlineStr"/>
       <c r="H70" s="7" t="inlineStr"/>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr"/>
+      <c r="J70" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="J70" s="7" t="inlineStr">
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K70" s="7" t="inlineStr">
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L70" s="7" t="inlineStr">
+      <c r="M70" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M70" s="7" t="inlineStr">
+      <c r="N70" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -9607,15 +9794,16 @@
       <c r="F71" s="9" t="inlineStr"/>
       <c r="G71" s="9" t="inlineStr"/>
       <c r="H71" s="9" t="inlineStr"/>
-      <c r="I71" s="9" t="inlineStr">
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>&amp;kp LS(LEFT)</t>
         </is>
       </c>
-      <c r="J71" s="9" t="inlineStr"/>
       <c r="K71" s="9" t="inlineStr"/>
       <c r="L71" s="9" t="inlineStr"/>
-      <c r="M71" s="9" t="inlineStr">
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -9666,29 +9854,35 @@
       <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J72" s="7" t="inlineStr">
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K72" s="7" t="inlineStr">
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L72" s="7" t="inlineStr">
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M72" s="7" t="inlineStr">
+      <c r="N72" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -9716,7 +9910,8 @@
       <c r="J73" s="9" t="inlineStr"/>
       <c r="K73" s="9" t="inlineStr"/>
       <c r="L73" s="9" t="inlineStr"/>
-      <c r="M73" s="9" t="inlineStr">
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -9767,29 +9962,25 @@
       <c r="H74" s="7" t="inlineStr"/>
       <c r="I74" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K74" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M74" s="7" t="inlineStr">
+      <c r="N74" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -9814,6 +10005,7 @@
       <c r="K75" s="9" t="inlineStr"/>
       <c r="L75" s="9" t="inlineStr"/>
       <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -9832,7 +10024,8 @@
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
-      <c r="M76" s="5" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="5" t="n"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
@@ -9872,31 +10065,32 @@
       </c>
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;kp F6</t>
         </is>
       </c>
-      <c r="J77" s="7" t="inlineStr">
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;kp F7</t>
         </is>
       </c>
-      <c r="K77" s="7" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;kp F8</t>
         </is>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="M77" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;kp F9</t>
         </is>
       </c>
-      <c r="M77" s="7" t="inlineStr">
+      <c r="N77" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;kp F10</t>
@@ -9936,27 +10130,28 @@
       </c>
       <c r="G78" s="9" t="inlineStr"/>
       <c r="H78" s="9" t="inlineStr"/>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F6</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F7</t>
         </is>
       </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F8</t>
         </is>
       </c>
-      <c r="L78" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F9</t>
         </is>
       </c>
-      <c r="M78" s="9" t="inlineStr">
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F10</t>
         </is>
@@ -10000,31 +10195,32 @@
       </c>
       <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr"/>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J79" s="7" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K79" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;sys_reset</t>
         </is>
       </c>
-      <c r="M79" s="7" t="inlineStr">
+      <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -10051,12 +10247,13 @@
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
-      <c r="L80" s="9" t="inlineStr">
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -10103,29 +10300,35 @@
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;bootloader</t>
         </is>
       </c>
-      <c r="J81" s="7" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K81" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L81" s="7" t="inlineStr">
+      <c r="M81" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M81" s="7" t="inlineStr">
+      <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -10149,15 +10352,16 @@
       </c>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
-      <c r="I82" s="9" t="inlineStr">
+      <c r="I82" s="9" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>&amp;bootloader</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -10204,29 +10408,25 @@
       <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J83" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M83" s="7" t="inlineStr">
+      <c r="N83" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -10251,6 +10451,7 @@
       <c r="K84" s="9" t="inlineStr"/>
       <c r="L84" s="9" t="inlineStr"/>
       <c r="M84" s="9" t="inlineStr"/>
+      <c r="N84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -10269,7 +10470,8 @@
       <c r="J85" s="4" t="n"/>
       <c r="K85" s="4" t="n"/>
       <c r="L85" s="4" t="n"/>
-      <c r="M85" s="5" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="5" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -10309,31 +10511,32 @@
       </c>
       <c r="G86" s="7" t="inlineStr"/>
       <c r="H86" s="7" t="inlineStr"/>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="J86" s="7" t="inlineStr">
+      <c r="K86" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;out OUT_USB</t>
         </is>
       </c>
-      <c r="K86" s="7" t="inlineStr">
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L86" s="7" t="inlineStr">
+      <c r="M86" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M86" s="7" t="inlineStr">
+      <c r="N86" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -10374,14 +10577,15 @@
       <c r="G87" s="9" t="inlineStr"/>
       <c r="H87" s="9" t="inlineStr"/>
       <c r="I87" s="9" t="inlineStr"/>
-      <c r="J87" s="9" t="inlineStr">
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr">
         <is>
           <t>&amp;out OUT_USB</t>
         </is>
       </c>
-      <c r="K87" s="9" t="inlineStr"/>
       <c r="L87" s="9" t="inlineStr"/>
       <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="9" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
@@ -10421,31 +10625,32 @@
       </c>
       <c r="G88" s="7" t="inlineStr"/>
       <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J88" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K88" s="7" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L88" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M88" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;none</t>
@@ -10474,6 +10679,7 @@
       <c r="K89" s="9" t="inlineStr"/>
       <c r="L89" s="9" t="inlineStr"/>
       <c r="M89" s="9" t="inlineStr"/>
+      <c r="N89" s="9" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
@@ -10520,29 +10726,35 @@
       <c r="H90" s="7" t="inlineStr"/>
       <c r="I90" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J90" s="7" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K90" s="7" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L90" s="7" t="inlineStr">
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M90" s="7" t="inlineStr">
+      <c r="N90" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;none</t>
@@ -10575,6 +10787,7 @@
       <c r="K91" s="9" t="inlineStr"/>
       <c r="L91" s="9" t="inlineStr"/>
       <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="9" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
@@ -10621,29 +10834,25 @@
       <c r="H92" s="7" t="inlineStr"/>
       <c r="I92" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J92" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K92" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M92" s="7" t="inlineStr">
+      <c r="N92" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -10668,6 +10877,7 @@
       <c r="K93" s="9" t="inlineStr"/>
       <c r="L93" s="9" t="inlineStr"/>
       <c r="M93" s="9" t="inlineStr"/>
+      <c r="N93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -10686,7 +10896,8 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="4" t="n"/>
-      <c r="M94" s="5" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="5" t="n"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
@@ -10726,31 +10937,32 @@
       </c>
       <c r="G95" s="7" t="inlineStr"/>
       <c r="H95" s="7" t="inlineStr"/>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="J95" s="7" t="inlineStr">
+      <c r="K95" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K95" s="7" t="inlineStr">
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L95" s="7" t="inlineStr">
+      <c r="M95" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M95" s="7" t="inlineStr">
+      <c r="N95" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -10775,6 +10987,7 @@
       <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
+      <c r="N96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
@@ -10814,31 +11027,32 @@
       </c>
       <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J97" s="7" t="inlineStr">
+      <c r="K97" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;none</t>
         </is>
       </c>
-      <c r="K97" s="7" t="inlineStr">
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
-      <c r="L97" s="7" t="inlineStr">
+      <c r="M97" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;none</t>
         </is>
       </c>
-      <c r="M97" s="7" t="inlineStr">
+      <c r="N97" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;trans</t>
@@ -10868,13 +11082,14 @@
       <c r="H98" s="9" t="inlineStr"/>
       <c r="I98" s="9" t="inlineStr"/>
       <c r="J98" s="9" t="inlineStr"/>
-      <c r="K98" s="9" t="inlineStr">
+      <c r="K98" s="9" t="inlineStr"/>
+      <c r="L98" s="9" t="inlineStr">
         <is>
           <t>&amp;mo MOUSE_SCROLL</t>
         </is>
       </c>
-      <c r="L98" s="9" t="inlineStr"/>
-      <c r="M98" s="9" t="inlineStr">
+      <c r="M98" s="9" t="inlineStr"/>
+      <c r="N98" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -10925,29 +11140,35 @@
       <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J99" s="7" t="inlineStr">
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;none</t>
         </is>
       </c>
-      <c r="K99" s="7" t="inlineStr">
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L99" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;none</t>
         </is>
       </c>
-      <c r="M99" s="7" t="inlineStr">
+      <c r="N99" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;trans</t>
@@ -10975,7 +11196,8 @@
       <c r="J100" s="9" t="inlineStr"/>
       <c r="K100" s="9" t="inlineStr"/>
       <c r="L100" s="9" t="inlineStr"/>
-      <c r="M100" s="9" t="inlineStr">
+      <c r="M100" s="9" t="inlineStr"/>
+      <c r="N100" s="9" t="inlineStr">
         <is>
           <t>▽</t>
         </is>
@@ -11026,29 +11248,25 @@
       <c r="H101" s="7" t="inlineStr"/>
       <c r="I101" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J101" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K101" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L101" s="7" t="inlineStr">
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M101" s="7" t="inlineStr">
+      <c r="N101" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -11081,6 +11299,7 @@
       <c r="K102" s="9" t="inlineStr"/>
       <c r="L102" s="9" t="inlineStr"/>
       <c r="M102" s="9" t="inlineStr"/>
+      <c r="N102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -11099,7 +11318,8 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
       <c r="L103" s="4" t="n"/>
-      <c r="M103" s="5" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="5" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
@@ -11139,31 +11359,32 @@
       </c>
       <c r="G104" s="7" t="inlineStr"/>
       <c r="H104" s="7" t="inlineStr"/>
-      <c r="I104" s="7" t="inlineStr">
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>pos 5
 &amp;none</t>
         </is>
       </c>
-      <c r="J104" s="7" t="inlineStr">
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>pos 6
 &amp;none</t>
         </is>
       </c>
-      <c r="K104" s="7" t="inlineStr">
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>pos 7
 &amp;none</t>
         </is>
       </c>
-      <c r="L104" s="7" t="inlineStr">
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>pos 8
 &amp;none</t>
         </is>
       </c>
-      <c r="M104" s="7" t="inlineStr">
+      <c r="N104" s="7" t="inlineStr">
         <is>
           <t>pos 9
 &amp;none</t>
@@ -11188,6 +11409,7 @@
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
       <c r="M105" s="9" t="inlineStr"/>
+      <c r="N105" s="9" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
@@ -11227,31 +11449,32 @@
       </c>
       <c r="G106" s="7" t="inlineStr"/>
       <c r="H106" s="7" t="inlineStr"/>
-      <c r="I106" s="7" t="inlineStr">
+      <c r="I106" s="7" t="inlineStr"/>
+      <c r="J106" s="7" t="inlineStr">
         <is>
           <t>pos 15
 &amp;none</t>
         </is>
       </c>
-      <c r="J106" s="7" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>pos 16
 &amp;mkp MB1</t>
         </is>
       </c>
-      <c r="K106" s="7" t="inlineStr">
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>pos 17
 &amp;none</t>
         </is>
       </c>
-      <c r="L106" s="7" t="inlineStr">
+      <c r="M106" s="7" t="inlineStr">
         <is>
           <t>pos 18
 &amp;mkp MB2</t>
         </is>
       </c>
-      <c r="M106" s="7" t="inlineStr">
+      <c r="N106" s="7" t="inlineStr">
         <is>
           <t>pos 19
 &amp;kp RCTRL</t>
@@ -11284,18 +11507,19 @@
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="inlineStr"/>
       <c r="I107" s="9" t="inlineStr"/>
-      <c r="J107" s="9" t="inlineStr">
+      <c r="J107" s="9" t="inlineStr"/>
+      <c r="K107" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB1</t>
         </is>
       </c>
-      <c r="K107" s="9" t="inlineStr"/>
-      <c r="L107" s="9" t="inlineStr">
+      <c r="L107" s="9" t="inlineStr"/>
+      <c r="M107" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="M107" s="9" t="inlineStr">
+      <c r="N107" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RCTRL</t>
         </is>
@@ -11346,29 +11570,35 @@
       <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="7" t="inlineStr">
         <is>
+          <t>pos 38
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
           <t>pos 26
 &amp;none</t>
         </is>
       </c>
-      <c r="J108" s="7" t="inlineStr">
+      <c r="K108" s="7" t="inlineStr">
         <is>
           <t>pos 27
 &amp;mkp MB4</t>
         </is>
       </c>
-      <c r="K108" s="7" t="inlineStr">
+      <c r="L108" s="7" t="inlineStr">
         <is>
           <t>pos 28
 &amp;none</t>
         </is>
       </c>
-      <c r="L108" s="7" t="inlineStr">
+      <c r="M108" s="7" t="inlineStr">
         <is>
           <t>pos 29
 &amp;mkp MB5</t>
         </is>
       </c>
-      <c r="M108" s="7" t="inlineStr">
+      <c r="N108" s="7" t="inlineStr">
         <is>
           <t>pos 30
 &amp;kp RIGHT_SHIFT</t>
@@ -11401,18 +11631,19 @@
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="inlineStr"/>
       <c r="I109" s="9" t="inlineStr"/>
-      <c r="J109" s="9" t="inlineStr">
+      <c r="J109" s="9" t="inlineStr"/>
+      <c r="K109" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB4</t>
         </is>
       </c>
-      <c r="K109" s="9" t="inlineStr"/>
-      <c r="L109" s="9" t="inlineStr">
+      <c r="L109" s="9" t="inlineStr"/>
+      <c r="M109" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB5</t>
         </is>
       </c>
-      <c r="M109" s="9" t="inlineStr">
+      <c r="N109" s="9" t="inlineStr">
         <is>
           <t>&amp;kp RIGHT_SHIFT</t>
         </is>
@@ -11463,29 +11694,25 @@
       <c r="H110" s="7" t="inlineStr"/>
       <c r="I110" s="7" t="inlineStr">
         <is>
+          <t>pos 39
+&amp;none</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
           <t>pos 37
 &amp;none</t>
         </is>
       </c>
-      <c r="J110" s="7" t="inlineStr">
-        <is>
-          <t>pos 38
-&amp;none</t>
-        </is>
-      </c>
-      <c r="K110" s="7" t="inlineStr">
-        <is>
-          <t>pos 39
-&amp;none</t>
-        </is>
-      </c>
-      <c r="L110" s="7" t="inlineStr">
+      <c r="K110" s="7" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr">
         <is>
           <t>pos 40
 &amp;none</t>
         </is>
       </c>
-      <c r="M110" s="7" t="inlineStr">
+      <c r="N110" s="7" t="inlineStr">
         <is>
           <t>pos 41
 &amp;none</t>
@@ -11518,19 +11745,20 @@
       <c r="K111" s="9" t="inlineStr"/>
       <c r="L111" s="9" t="inlineStr"/>
       <c r="M111" s="9" t="inlineStr"/>
+      <c r="N111" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A76:M76"/>
-    <mergeCell ref="A66:M66"/>
-    <mergeCell ref="A45:M45"/>
-    <mergeCell ref="A94:M94"/>
-    <mergeCell ref="A103:M103"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="A85:M85"/>
-    <mergeCell ref="A28:M28"/>
+    <mergeCell ref="A55:N55"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="A76:N76"/>
+    <mergeCell ref="A85:N85"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="A103:N103"/>
+    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A94:N94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4524,7 +4524,7 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -4536,19 +4536,19 @@
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -4591,15 +4591,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>CAPSLOCK</t>
+        </is>
+      </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
@@ -4611,7 +4627,11 @@
           <t>リセット</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4622,7 +4642,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4634,7 +4654,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4689,7 +4709,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -4699,9 +4719,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
       <c r="F82" s="9" t="inlineStr">
         <is>
@@ -4719,7 +4747,11 @@
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -10166,7 +10198,7 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -10178,19 +10210,19 @@
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -10223,7 +10255,7 @@
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -10233,15 +10265,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp CAPSLOCK</t>
+        </is>
+      </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
@@ -10253,7 +10301,11 @@
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -10264,7 +10316,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -10276,7 +10328,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10331,7 +10383,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -10341,9 +10393,17 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
       <c r="F82" s="9" t="inlineStr">
         <is>
@@ -10361,7 +10421,11 @@
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4524,13 +4524,13 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4575,7 +4575,7 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
@@ -4591,16 +4591,8 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
           <t>PRINTSCREEN</t>
@@ -4622,11 +4614,7 @@
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="M80" s="9" t="inlineStr"/>
       <c r="N80" s="9" t="inlineStr">
         <is>
           <t>F11</t>
@@ -4666,7 +4654,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4685,7 +4673,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -4731,19 +4719,11 @@
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
@@ -10198,13 +10178,13 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>pos 10
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -10249,7 +10229,7 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
@@ -10265,16 +10245,8 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="B80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
           <t>&amp;kp PRINTSCREEN</t>
@@ -10296,11 +10268,7 @@
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="M80" s="9" t="inlineStr"/>
       <c r="N80" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F11</t>
@@ -10340,7 +10308,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -10359,7 +10327,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -10405,19 +10373,11 @@
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -4530,25 +4530,25 @@
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -4575,13 +4575,13 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -4592,26 +4592,34 @@
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr"/>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -4622,7 +4630,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -4634,7 +4642,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4646,7 +4654,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4665,7 +4673,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -4689,7 +4697,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -4699,27 +4707,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -10172,25 +10184,25 @@
       <c r="C79" s="7" t="inlineStr">
         <is>
           <t>pos 11
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
           <t>pos 12
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
           <t>pos 13
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>pos 14
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -10217,13 +10229,13 @@
       <c r="M79" s="7" t="inlineStr">
         <is>
           <t>pos 18
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
           <t>pos 19
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
     </row>
@@ -10234,26 +10246,34 @@
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr"/>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr"/>
       <c r="H80" s="9" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr"/>
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -10264,7 +10284,7 @@
       <c r="B81" s="7" t="inlineStr">
         <is>
           <t>pos 20
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -10276,7 +10296,7 @@
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>pos 22
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -10288,7 +10308,7 @@
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>pos 24
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -10307,7 +10327,7 @@
       <c r="J81" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -10331,7 +10351,7 @@
       <c r="N81" s="7" t="inlineStr">
         <is>
           <t>pos 30
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
     </row>
@@ -10341,27 +10361,31 @@
           <t>タップ</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr"/>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr"/>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="F82" s="9" t="inlineStr"/>
       <c r="G82" s="9" t="inlineStr"/>
       <c r="H82" s="9" t="inlineStr"/>
       <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="J82" s="9" t="inlineStr"/>
       <c r="K82" s="9" t="inlineStr"/>
       <c r="L82" s="9" t="inlineStr"/>
       <c r="M82" s="9" t="inlineStr"/>
-      <c r="N82" s="9" t="inlineStr"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
